--- a/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Summary_Statistics_h1.xlsx
+++ b/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Summary_Statistics_h1.xlsx
@@ -480,34 +480,34 @@
         <v>15</v>
       </c>
       <c r="C2">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E2">
         <v>0.6888</v>
       </c>
       <c r="F2">
-        <v>0.9828</v>
+        <v>1.1231</v>
       </c>
       <c r="G2">
-        <v>0.2941</v>
+        <v>0.4344</v>
       </c>
       <c r="H2">
-        <v>2.9536</v>
+        <v>4.2064</v>
       </c>
       <c r="I2">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="J2">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="K2">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="M2">
         <v>51</v>
@@ -524,37 +524,37 @@
         <v>16</v>
       </c>
       <c r="C3">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.638</v>
+        <v>0.7134</v>
       </c>
       <c r="F3">
-        <v>0.8977000000000001</v>
+        <v>0.9635</v>
       </c>
       <c r="G3">
-        <v>0.2597</v>
+        <v>0.2502</v>
       </c>
       <c r="H3">
-        <v>2.3659</v>
+        <v>2.8874</v>
       </c>
       <c r="I3">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K3">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="L3">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="N3">
         <v>1</v>
@@ -571,34 +571,34 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>0.8372000000000001</v>
+        <v>0.6473</v>
       </c>
       <c r="F4">
-        <v>1.2319</v>
+        <v>1.3919</v>
       </c>
       <c r="G4">
-        <v>0.3947</v>
+        <v>0.7446</v>
       </c>
       <c r="H4">
-        <v>4.6717</v>
+        <v>6.428</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J4">
+        <v>15</v>
+      </c>
+      <c r="K4">
+        <v>11</v>
+      </c>
+      <c r="L4">
         <v>8</v>
       </c>
-      <c r="K4">
-        <v>6</v>
-      </c>
-      <c r="L4">
-        <v>7</v>
-      </c>
       <c r="M4">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="N4">
         <v>1</v>
